--- a/12622534 (4).xlsx
+++ b/12622534 (4).xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>I practiced SQL today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I started preparing for CA1 </t>
   </si>
 </sst>
 </file>
@@ -1157,26 +1160,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="17"/>
+      <c r="A9" s="18">
+        <v>46262</v>
+      </c>
+      <c r="B9" s="19">
+        <v>480</v>
+      </c>
+      <c r="C9" s="19">
+        <v>30</v>
+      </c>
+      <c r="D9" s="19">
+        <v>90</v>
+      </c>
+      <c r="E9" s="19">
+        <v>60</v>
+      </c>
+      <c r="F9" s="19">
+        <v>150</v>
+      </c>
+      <c r="G9" s="19">
+        <v>3</v>
+      </c>
+      <c r="H9" s="19">
+        <v>120</v>
+      </c>
+      <c r="I9" s="15">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J9" s="15">
+        <f t="shared" si="1"/>
+        <v>510</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1">
       <c r="A10" s="18"/>

--- a/12622534 (4).xlsx
+++ b/12622534 (4).xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t xml:space="preserve">I started preparing for CA1 </t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I practiced C today </t>
   </si>
 </sst>
 </file>
@@ -1206,26 +1212,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="17"/>
+      <c r="A10" s="18">
+        <v>46263</v>
+      </c>
+      <c r="B10" s="19">
+        <v>460</v>
+      </c>
+      <c r="C10" s="19">
+        <v>45</v>
+      </c>
+      <c r="D10" s="19">
+        <v>100</v>
+      </c>
+      <c r="E10" s="19">
+        <v>60</v>
+      </c>
+      <c r="F10" s="19">
+        <v>0</v>
+      </c>
+      <c r="G10" s="19">
+        <v>0</v>
+      </c>
+      <c r="H10" s="19">
+        <v>120</v>
+      </c>
+      <c r="I10" s="15">
+        <f t="shared" si="0"/>
+        <v>785</v>
+      </c>
+      <c r="J10" s="15">
+        <f t="shared" si="1"/>
+        <v>655</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1">
       <c r="A11" s="18"/>

--- a/12622534 (4).xlsx
+++ b/12622534 (4).xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t xml:space="preserve">I practiced C today </t>
+  </si>
+  <si>
+    <t>I studied SQL and python today</t>
   </si>
 </sst>
 </file>
@@ -1258,26 +1261,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="17"/>
+      <c r="A11" s="18">
+        <v>46264</v>
+      </c>
+      <c r="B11" s="19">
+        <v>460</v>
+      </c>
+      <c r="C11" s="19">
+        <v>60</v>
+      </c>
+      <c r="D11" s="19">
+        <v>120</v>
+      </c>
+      <c r="E11" s="19">
+        <v>30</v>
+      </c>
+      <c r="F11" s="19">
+        <v>0</v>
+      </c>
+      <c r="G11" s="19">
+        <v>0</v>
+      </c>
+      <c r="H11" s="19">
+        <v>90</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J11" s="15">
+        <f t="shared" si="1"/>
+        <v>680</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1">
       <c r="A12" s="18"/>

--- a/12622534 (4).xlsx
+++ b/12622534 (4).xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -210,6 +210,12 @@
   </si>
   <si>
     <t>I studied SQL and python today</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>prepared for CA1</t>
   </si>
 </sst>
 </file>
@@ -1307,26 +1313,48 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A12" s="18"/>
+      <c r="A12" s="18">
+        <v>46265</v>
+      </c>
       <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="17"/>
+      <c r="C12" s="19">
+        <v>30</v>
+      </c>
+      <c r="D12" s="19">
+        <v>90</v>
+      </c>
+      <c r="E12" s="19">
+        <v>30</v>
+      </c>
+      <c r="F12" s="19">
+        <v>250</v>
+      </c>
+      <c r="G12" s="19">
+        <v>5</v>
+      </c>
+      <c r="H12" s="19">
+        <v>120</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" si="0"/>
+        <v>520</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" si="1"/>
+        <v>920</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1">
       <c r="A13" s="18"/>

--- a/12622534 (4).xlsx
+++ b/12622534 (4).xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>prepared for CA1</t>
+  </si>
+  <si>
+    <t>Today was CA1 of programming c</t>
   </si>
 </sst>
 </file>
@@ -1316,7 +1319,9 @@
       <c r="A12" s="18">
         <v>46265</v>
       </c>
-      <c r="B12" s="19"/>
+      <c r="B12" s="19">
+        <v>450</v>
+      </c>
       <c r="C12" s="19">
         <v>30</v>
       </c>
@@ -1337,11 +1342,11 @@
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>520</v>
+        <v>970</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>920</v>
+        <v>470</v>
       </c>
       <c r="K12" s="20" t="s">
         <v>65</v>
@@ -1357,26 +1362,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="17"/>
+      <c r="A13" s="18">
+        <v>46266</v>
+      </c>
+      <c r="B13" s="19">
+        <v>400</v>
+      </c>
+      <c r="C13" s="19">
+        <v>0</v>
+      </c>
+      <c r="D13" s="19">
+        <v>90</v>
+      </c>
+      <c r="E13" s="19">
+        <v>45</v>
+      </c>
+      <c r="F13" s="19">
+        <v>300</v>
+      </c>
+      <c r="G13" s="19">
+        <v>6</v>
+      </c>
+      <c r="H13" s="19">
+        <v>60</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" si="0"/>
+        <v>895</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="1"/>
+        <v>545</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1">
       <c r="A14" s="18"/>

--- a/12622534 (4).xlsx
+++ b/12622534 (4).xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>Today was CA1 of programming c</t>
+  </si>
+  <si>
+    <t>I was late for the class</t>
   </si>
 </sst>
 </file>
@@ -1408,26 +1411,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="17"/>
+      <c r="A14" s="18">
+        <v>46267</v>
+      </c>
+      <c r="B14" s="19">
+        <v>460</v>
+      </c>
+      <c r="C14" s="19">
+        <v>30</v>
+      </c>
+      <c r="D14" s="19">
+        <v>80</v>
+      </c>
+      <c r="E14" s="19">
+        <v>30</v>
+      </c>
+      <c r="F14" s="19">
+        <v>4</v>
+      </c>
+      <c r="G14" s="19">
+        <v>200</v>
+      </c>
+      <c r="H14" s="19">
+        <v>50</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" si="0"/>
+        <v>654</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="1"/>
+        <v>786</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1">
       <c r="A15" s="18"/>

--- a/12622534 (4).xlsx
+++ b/12622534 (4).xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>I was late for the class</t>
+  </si>
+  <si>
+    <t>too many breaks after classes</t>
   </si>
 </sst>
 </file>
@@ -1457,26 +1460,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="17"/>
+      <c r="A15" s="18">
+        <v>46268</v>
+      </c>
+      <c r="B15" s="19">
+        <v>420</v>
+      </c>
+      <c r="C15" s="19">
+        <v>30</v>
+      </c>
+      <c r="D15" s="19">
+        <v>90</v>
+      </c>
+      <c r="E15" s="19">
+        <v>45</v>
+      </c>
+      <c r="F15" s="19">
+        <v>5</v>
+      </c>
+      <c r="G15" s="19">
+        <v>250</v>
+      </c>
+      <c r="H15" s="19">
+        <v>120</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="1"/>
+        <v>730</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1">
       <c r="A16" s="18"/>

--- a/12622534 (4).xlsx
+++ b/12622534 (4).xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -225,6 +225,12 @@
   </si>
   <si>
     <t>too many breaks after classes</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>I was bit confused in maths class</t>
   </si>
 </sst>
 </file>
@@ -1506,26 +1512,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="17"/>
+      <c r="A16" s="18">
+        <v>46269</v>
+      </c>
+      <c r="B16" s="19">
+        <v>460</v>
+      </c>
+      <c r="C16" s="19">
+        <v>40</v>
+      </c>
+      <c r="D16" s="19">
+        <v>120</v>
+      </c>
+      <c r="E16" s="19">
+        <v>90</v>
+      </c>
+      <c r="F16" s="19">
+        <v>5</v>
+      </c>
+      <c r="G16" s="19">
+        <v>250</v>
+      </c>
+      <c r="H16" s="19">
+        <v>90</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" si="0"/>
+        <v>805</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" si="1"/>
+        <v>635</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M16" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1">
       <c r="A17" s="18"/>

--- a/12622534 (4).xlsx
+++ b/12622534 (4).xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>I was bit confused in maths class</t>
+  </si>
+  <si>
+    <t>practiced SQL for CA1</t>
   </si>
 </sst>
 </file>
@@ -1558,26 +1561,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="17"/>
+      <c r="A17" s="18">
+        <v>46270</v>
+      </c>
+      <c r="B17" s="19">
+        <v>450</v>
+      </c>
+      <c r="C17" s="19">
+        <v>60</v>
+      </c>
+      <c r="D17" s="19">
+        <v>150</v>
+      </c>
+      <c r="E17" s="19">
+        <v>60</v>
+      </c>
+      <c r="F17" s="19">
+        <v>0</v>
+      </c>
+      <c r="G17" s="19">
+        <v>0</v>
+      </c>
+      <c r="H17" s="19">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J17" s="15">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1">
       <c r="A18" s="18"/>
